--- a/data/nzd0084/nzd0084.xlsx
+++ b/data/nzd0084/nzd0084.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F344"/>
+  <dimension ref="A1:F345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8692,6 +8692,30 @@
       <c r="F344" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>326.92</v>
+      </c>
+      <c r="C345" t="n">
+        <v>319.37</v>
+      </c>
+      <c r="D345" t="n">
+        <v>321.56</v>
+      </c>
+      <c r="E345" t="n">
+        <v>327.24</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8706,7 +8730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:B354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12239,6 +12263,16 @@
       </c>
       <c r="B353" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -12407,28 +12441,28 @@
         <v>0.0935</v>
       </c>
       <c r="I2" t="n">
-        <v>0.193182116692572</v>
+        <v>0.1871379074874703</v>
       </c>
       <c r="J2" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K2" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0451631141258223</v>
+        <v>0.04254863728651281</v>
       </c>
       <c r="M2" t="n">
-        <v>5.01976812805308</v>
+        <v>5.028804370557278</v>
       </c>
       <c r="N2" t="n">
-        <v>40.81474486455155</v>
+        <v>40.95040225292008</v>
       </c>
       <c r="O2" t="n">
-        <v>6.388641863851154</v>
+        <v>6.399250132079545</v>
       </c>
       <c r="P2" t="n">
-        <v>331.1494120143091</v>
+        <v>331.2143959069781</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12489,28 +12523,28 @@
         <v>0.0747</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2784274671258331</v>
+        <v>0.2700313261790829</v>
       </c>
       <c r="J3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K3" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08185236516525085</v>
+        <v>0.07712085611722974</v>
       </c>
       <c r="M3" t="n">
-        <v>5.333691385673151</v>
+        <v>5.351616321699524</v>
       </c>
       <c r="N3" t="n">
-        <v>44.98247816090986</v>
+        <v>45.3424367691063</v>
       </c>
       <c r="O3" t="n">
-        <v>6.706897804567315</v>
+        <v>6.733679289148415</v>
       </c>
       <c r="P3" t="n">
-        <v>324.974515146438</v>
+        <v>325.0647856687848</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12571,28 +12605,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2731965729210505</v>
+        <v>0.2647239419270632</v>
       </c>
       <c r="J4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K4" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07805916565935755</v>
+        <v>0.07340563903167296</v>
       </c>
       <c r="M4" t="n">
-        <v>5.381696862263831</v>
+        <v>5.401437144258704</v>
       </c>
       <c r="N4" t="n">
-        <v>45.60028721635187</v>
+        <v>45.96743168396514</v>
       </c>
       <c r="O4" t="n">
-        <v>6.752798472955629</v>
+        <v>6.779928589886853</v>
       </c>
       <c r="P4" t="n">
-        <v>327.4284999147162</v>
+        <v>327.5195928144577</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12649,28 +12683,28 @@
         <v>0.0931</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1583656639096986</v>
+        <v>0.1508014021521459</v>
       </c>
       <c r="J5" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K5" t="n">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03173037936884837</v>
+        <v>0.02878414288592079</v>
       </c>
       <c r="M5" t="n">
-        <v>5.032015925005833</v>
+        <v>5.047951841430387</v>
       </c>
       <c r="N5" t="n">
-        <v>39.58959245127485</v>
+        <v>39.87280509531982</v>
       </c>
       <c r="O5" t="n">
-        <v>6.292026100651113</v>
+        <v>6.314491673549013</v>
       </c>
       <c r="P5" t="n">
-        <v>334.7723593098724</v>
+        <v>334.85368594128</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12708,7 +12742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F344"/>
+  <dimension ref="A1:F345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23719,6 +23753,38 @@
         </is>
       </c>
     </row>
+    <row r="345">
+      <c r="A345" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>-35.507943304372056,174.47266040098003</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>-35.508586244919684,174.47309829407564</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>-35.50917905415525,174.4736243503743</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>-35.50975389727424,174.47418199755023</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0084/nzd0084.xlsx
+++ b/data/nzd0084/nzd0084.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F345"/>
+  <dimension ref="A1:F347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8714,6 +8714,54 @@
         <v>327.24</v>
       </c>
       <c r="F345" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>327.61</v>
+      </c>
+      <c r="C346" t="n">
+        <v>320.58</v>
+      </c>
+      <c r="D346" t="n">
+        <v>321.61</v>
+      </c>
+      <c r="E346" t="n">
+        <v>323.16</v>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="C347" t="n">
+        <v>322.93</v>
+      </c>
+      <c r="D347" t="n">
+        <v>322.05</v>
+      </c>
+      <c r="E347" t="n">
+        <v>325.27</v>
+      </c>
+      <c r="F347" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8730,7 +8778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B354"/>
+  <dimension ref="A1:B356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12273,6 +12321,26 @@
       </c>
       <c r="B354" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -12441,28 +12509,28 @@
         <v>0.0935</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1871379074874703</v>
+        <v>0.1773928022164249</v>
       </c>
       <c r="J2" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K2" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04254863728651281</v>
+        <v>0.03863793266475801</v>
       </c>
       <c r="M2" t="n">
-        <v>5.028804370557278</v>
+        <v>5.037766364376338</v>
       </c>
       <c r="N2" t="n">
-        <v>40.95040225292008</v>
+        <v>41.05337766641195</v>
       </c>
       <c r="O2" t="n">
-        <v>6.399250132079545</v>
+        <v>6.407290977192463</v>
       </c>
       <c r="P2" t="n">
-        <v>331.2143959069781</v>
+        <v>331.3194565319238</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12523,28 +12591,28 @@
         <v>0.0747</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2700313261790829</v>
+        <v>0.2566484946995825</v>
       </c>
       <c r="J3" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K3" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07712085611722974</v>
+        <v>0.07023538548993458</v>
       </c>
       <c r="M3" t="n">
-        <v>5.351616321699524</v>
+        <v>5.374776548140127</v>
       </c>
       <c r="N3" t="n">
-        <v>45.3424367691063</v>
+        <v>45.71916513141202</v>
       </c>
       <c r="O3" t="n">
-        <v>6.733679289148415</v>
+        <v>6.761594865962617</v>
       </c>
       <c r="P3" t="n">
-        <v>325.0647856687848</v>
+        <v>325.2090648007505</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12605,28 +12673,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2647239419270632</v>
+        <v>0.2484957717390047</v>
       </c>
       <c r="J4" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K4" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07340563903167296</v>
+        <v>0.06492710836182725</v>
       </c>
       <c r="M4" t="n">
-        <v>5.401437144258704</v>
+        <v>5.438034557561325</v>
       </c>
       <c r="N4" t="n">
-        <v>45.96743168396514</v>
+        <v>46.62954928519513</v>
       </c>
       <c r="O4" t="n">
-        <v>6.779928589886853</v>
+        <v>6.828583256078463</v>
       </c>
       <c r="P4" t="n">
-        <v>327.5195928144577</v>
+        <v>327.6945538940743</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12683,28 +12751,28 @@
         <v>0.0931</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1508014021521459</v>
+        <v>0.1321814911091335</v>
       </c>
       <c r="J5" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K5" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02878414288592079</v>
+        <v>0.02192369731116395</v>
       </c>
       <c r="M5" t="n">
-        <v>5.047951841430387</v>
+        <v>5.093998690521529</v>
       </c>
       <c r="N5" t="n">
-        <v>39.87280509531982</v>
+        <v>40.86994358161439</v>
       </c>
       <c r="O5" t="n">
-        <v>6.314491673549013</v>
+        <v>6.392960470831522</v>
       </c>
       <c r="P5" t="n">
-        <v>334.85368594128</v>
+        <v>335.0544287400353</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12742,7 +12810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F345"/>
+  <dimension ref="A1:F347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23785,6 +23853,70 @@
         </is>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>-35.50793975330268,174.4726666466103</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>-35.50858001765797,174.47310924662168</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>-35.509178796829076,174.47362480296096</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>-35.50977489519877,174.4741450663141</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>-35.50793002645887,174.47268375420344</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>-35.5085679233866,174.47313051809053</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>-35.50917653235886,174.47362878572355</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>-35.50976403597936,174.47416416555873</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0084/nzd0084.xlsx
+++ b/data/nzd0084/nzd0084.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F347"/>
+  <dimension ref="A1:F348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8762,6 +8762,30 @@
         <v>325.27</v>
       </c>
       <c r="F347" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>329.77</v>
+      </c>
+      <c r="C348" t="n">
+        <v>323.71</v>
+      </c>
+      <c r="D348" t="n">
+        <v>324.05</v>
+      </c>
+      <c r="E348" t="n">
+        <v>327.92</v>
+      </c>
+      <c r="F348" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8778,7 +8802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B356"/>
+  <dimension ref="A1:B357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12341,6 +12365,16 @@
       </c>
       <c r="B356" t="n">
         <v>0.48</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>-0.44</v>
       </c>
     </row>
   </sheetData>
@@ -12509,28 +12543,28 @@
         <v>0.0935</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1773928022164249</v>
+        <v>0.1733874533198896</v>
       </c>
       <c r="J2" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K2" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03863793266475801</v>
+        <v>0.03714012437279179</v>
       </c>
       <c r="M2" t="n">
-        <v>5.037766364376338</v>
+        <v>5.038764700480673</v>
       </c>
       <c r="N2" t="n">
-        <v>41.05337766641195</v>
+        <v>41.04930822363096</v>
       </c>
       <c r="O2" t="n">
-        <v>6.407290977192463</v>
+        <v>6.406973405878236</v>
       </c>
       <c r="P2" t="n">
-        <v>331.3194565319238</v>
+        <v>331.3627949105102</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -12591,28 +12625,28 @@
         <v>0.0747</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2566484946995825</v>
+        <v>0.2513252490958038</v>
       </c>
       <c r="J3" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K3" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07023538548993458</v>
+        <v>0.06773300042417651</v>
       </c>
       <c r="M3" t="n">
-        <v>5.374776548140127</v>
+        <v>5.380768238147726</v>
       </c>
       <c r="N3" t="n">
-        <v>45.71916513141202</v>
+        <v>45.78919536955189</v>
       </c>
       <c r="O3" t="n">
-        <v>6.761594865962617</v>
+        <v>6.766771414016576</v>
       </c>
       <c r="P3" t="n">
-        <v>325.2090648007505</v>
+        <v>325.2666629873864</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -12673,28 +12707,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2484957717390047</v>
+        <v>0.2419496865460373</v>
       </c>
       <c r="J4" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K4" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06492710836182725</v>
+        <v>0.06180789204505399</v>
       </c>
       <c r="M4" t="n">
-        <v>5.438034557561325</v>
+        <v>5.449992276752308</v>
       </c>
       <c r="N4" t="n">
-        <v>46.62954928519513</v>
+        <v>46.80031135045807</v>
       </c>
       <c r="O4" t="n">
-        <v>6.828583256078463</v>
+        <v>6.841075306591653</v>
       </c>
       <c r="P4" t="n">
-        <v>327.6945538940743</v>
+        <v>327.7653833587926</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -12751,28 +12785,28 @@
         <v>0.0931</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1321814911091335</v>
+        <v>0.1254146382180358</v>
       </c>
       <c r="J5" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K5" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02192369731116395</v>
+        <v>0.01976807238088762</v>
       </c>
       <c r="M5" t="n">
-        <v>5.093998690521529</v>
+        <v>5.107801357102315</v>
       </c>
       <c r="N5" t="n">
-        <v>40.86994358161439</v>
+        <v>41.07823286020457</v>
       </c>
       <c r="O5" t="n">
-        <v>6.392960470831522</v>
+        <v>6.40923028609556</v>
       </c>
       <c r="P5" t="n">
-        <v>335.0544287400353</v>
+        <v>335.1276469390007</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -12810,7 +12844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F347"/>
+  <dimension ref="A1:F348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23917,6 +23951,38 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>-35.507928636909575,174.47268619814497</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>-35.508563909117015,174.47313757840644</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>-35.509166239310844,174.47364688918697</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-35.50975039761908,174.47418815275435</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
